--- a/modulos/normativos/NORMATIVOS_ESGILA.xlsx
+++ b/modulos/normativos/NORMATIVOS_ESGILA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manu/Desktop/ESGILA/modulos/normativos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ED3A091-A0C9-6844-9778-812D75F93A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C82511-AE4E-6845-A027-336DF4C6BE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -882,9 +882,6 @@
     <t>ELEMENTOS EN SUSPENSION</t>
   </si>
   <si>
-    <t>CONSOLIDADO GENERAL DE NORMATIVOS AKC</t>
-  </si>
-  <si>
     <t>Atleta</t>
   </si>
   <si>
@@ -999,9 +996,6 @@
     <t>Salvada desdé gigante</t>
   </si>
   <si>
-    <t>INDICADORES DE SEGUIMIENTO AKC</t>
-  </si>
-  <si>
     <t>Atletas evaluados</t>
   </si>
   <si>
@@ -1076,6 +1070,12 @@
   </si>
   <si>
     <t>Elementos</t>
+  </si>
+  <si>
+    <t>CONSOLIDADO GENERAL DE NORMATIVOS ESGILA</t>
+  </si>
+  <si>
+    <t>INDICADORES DE SEGUIMIENTO ESGILA</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1215,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1518,11 +1518,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1635,6 +1657,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1643,15 +1674,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1676,11 +1698,20 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1734,6 +1765,51 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor auto="1"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2675,13 +2751,13 @@
     <row r="1" spans="1:26" s="8" customFormat="1" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19"/>
       <c r="B1" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1" s="21" t="s">
         <v>325</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>327</v>
       </c>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
@@ -2707,37 +2783,37 @@
       <c r="Z1" s="21"/>
     </row>
     <row r="2" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="51"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="48"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="22" t="s">
@@ -2817,7 +2893,7 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -2895,7 +2971,7 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A5" s="47"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -2973,7 +3049,7 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A6" s="47"/>
+      <c r="A6" s="50"/>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
@@ -3051,7 +3127,7 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7" s="47"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
@@ -3129,7 +3205,7 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A8" s="47"/>
+      <c r="A8" s="50"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3207,7 +3283,7 @@
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A9" s="47"/>
+      <c r="A9" s="50"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3285,7 +3361,7 @@
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A10" s="47"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
@@ -3363,7 +3439,7 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A11" s="47"/>
+      <c r="A11" s="50"/>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
@@ -3441,7 +3517,7 @@
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A12" s="47"/>
+      <c r="A12" s="50"/>
       <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
@@ -3519,7 +3595,7 @@
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A13" s="47"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
@@ -3597,7 +3673,7 @@
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A14" s="47"/>
+      <c r="A14" s="50"/>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
@@ -3675,7 +3751,7 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A15" s="47"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
@@ -3753,7 +3829,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="48"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="26" t="s">
         <v>17</v>
       </c>
@@ -3831,7 +3907,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="49" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="22" t="s">
@@ -3911,7 +3987,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A18" s="47"/>
+      <c r="A18" s="50"/>
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
@@ -3989,7 +4065,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A19" s="47"/>
+      <c r="A19" s="50"/>
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
@@ -4067,7 +4143,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A20" s="47"/>
+      <c r="A20" s="50"/>
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -4145,7 +4221,7 @@
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
@@ -4223,7 +4299,7 @@
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A22" s="47"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
@@ -4301,7 +4377,7 @@
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A23" s="47"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
@@ -4379,7 +4455,7 @@
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A24" s="47"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="2" t="s">
         <v>26</v>
       </c>
@@ -4457,7 +4533,7 @@
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A25" s="47"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="2" t="s">
         <v>27</v>
       </c>
@@ -4535,7 +4611,7 @@
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A26" s="47"/>
+      <c r="A26" s="50"/>
       <c r="B26" s="2" t="s">
         <v>28</v>
       </c>
@@ -4613,7 +4689,7 @@
       </c>
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="26" t="s">
         <v>29</v>
       </c>
@@ -4691,7 +4767,7 @@
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A28" s="46" t="s">
+      <c r="A28" s="49" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="22" t="s">
@@ -4771,7 +4847,7 @@
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A29" s="47"/>
+      <c r="A29" s="50"/>
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
@@ -4849,7 +4925,7 @@
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A30" s="47"/>
+      <c r="A30" s="50"/>
       <c r="B30" s="2" t="s">
         <v>33</v>
       </c>
@@ -4927,7 +5003,7 @@
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A31" s="47"/>
+      <c r="A31" s="50"/>
       <c r="B31" s="2" t="s">
         <v>34</v>
       </c>
@@ -5005,7 +5081,7 @@
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A32" s="47"/>
+      <c r="A32" s="50"/>
       <c r="B32" s="2" t="s">
         <v>35</v>
       </c>
@@ -5083,7 +5159,7 @@
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A33" s="47"/>
+      <c r="A33" s="50"/>
       <c r="B33" s="2" t="s">
         <v>36</v>
       </c>
@@ -5161,7 +5237,7 @@
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A34" s="47"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="2" t="s">
         <v>37</v>
       </c>
@@ -5239,7 +5315,7 @@
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A35" s="47"/>
+      <c r="A35" s="50"/>
       <c r="B35" s="2" t="s">
         <v>38</v>
       </c>
@@ -5317,7 +5393,7 @@
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A36" s="47"/>
+      <c r="A36" s="50"/>
       <c r="B36" s="2" t="s">
         <v>39</v>
       </c>
@@ -5395,7 +5471,7 @@
       </c>
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="48"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="26" t="s">
         <v>40</v>
       </c>
@@ -5473,7 +5549,7 @@
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A38" s="46" t="s">
+      <c r="A38" s="49" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="22" t="s">
@@ -5553,7 +5629,7 @@
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A39" s="47"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="2" t="s">
         <v>43</v>
       </c>
@@ -5631,7 +5707,7 @@
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A40" s="47"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="2" t="s">
         <v>44</v>
       </c>
@@ -5709,7 +5785,7 @@
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A41" s="47"/>
+      <c r="A41" s="50"/>
       <c r="B41" s="2" t="s">
         <v>45</v>
       </c>
@@ -5787,7 +5863,7 @@
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A42" s="47"/>
+      <c r="A42" s="50"/>
       <c r="B42" s="2" t="s">
         <v>46</v>
       </c>
@@ -5865,7 +5941,7 @@
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A43" s="47"/>
+      <c r="A43" s="50"/>
       <c r="B43" s="2" t="s">
         <v>47</v>
       </c>
@@ -5943,7 +6019,7 @@
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A44" s="47"/>
+      <c r="A44" s="50"/>
       <c r="B44" s="2" t="s">
         <v>48</v>
       </c>
@@ -6021,7 +6097,7 @@
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A45" s="47"/>
+      <c r="A45" s="50"/>
       <c r="B45" s="2" t="s">
         <v>49</v>
       </c>
@@ -6099,7 +6175,7 @@
       </c>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="48"/>
+      <c r="A46" s="51"/>
       <c r="B46" s="26" t="s">
         <v>50</v>
       </c>
@@ -6235,7 +6311,7 @@
       <c r="Z48" s="60"/>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A49" s="46" t="s">
+      <c r="A49" s="49" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="32" t="s">
@@ -6315,7 +6391,7 @@
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A50" s="47"/>
+      <c r="A50" s="50"/>
       <c r="B50" s="3" t="s">
         <v>54</v>
       </c>
@@ -6393,7 +6469,7 @@
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A51" s="47"/>
+      <c r="A51" s="50"/>
       <c r="B51" s="3" t="s">
         <v>55</v>
       </c>
@@ -6471,7 +6547,7 @@
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A52" s="47"/>
+      <c r="A52" s="50"/>
       <c r="B52" s="3" t="s">
         <v>56</v>
       </c>
@@ -6549,7 +6625,7 @@
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A53" s="47"/>
+      <c r="A53" s="50"/>
       <c r="B53" s="3" t="s">
         <v>57</v>
       </c>
@@ -6627,7 +6703,7 @@
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A54" s="47"/>
+      <c r="A54" s="50"/>
       <c r="B54" s="3" t="s">
         <v>58</v>
       </c>
@@ -6705,7 +6781,7 @@
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A55" s="47"/>
+      <c r="A55" s="50"/>
       <c r="B55" s="3" t="s">
         <v>59</v>
       </c>
@@ -6783,7 +6859,7 @@
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A56" s="47"/>
+      <c r="A56" s="50"/>
       <c r="B56" s="3" t="s">
         <v>60</v>
       </c>
@@ -6861,7 +6937,7 @@
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A57" s="47"/>
+      <c r="A57" s="50"/>
       <c r="B57" s="3" t="s">
         <v>61</v>
       </c>
@@ -6939,7 +7015,7 @@
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A58" s="47"/>
+      <c r="A58" s="50"/>
       <c r="B58" s="3" t="s">
         <v>62</v>
       </c>
@@ -7017,7 +7093,7 @@
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A59" s="47"/>
+      <c r="A59" s="50"/>
       <c r="B59" s="3" t="s">
         <v>63</v>
       </c>
@@ -7095,7 +7171,7 @@
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A60" s="47"/>
+      <c r="A60" s="50"/>
       <c r="B60" s="3" t="s">
         <v>64</v>
       </c>
@@ -7173,7 +7249,7 @@
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A61" s="47"/>
+      <c r="A61" s="50"/>
       <c r="B61" s="3" t="s">
         <v>65</v>
       </c>
@@ -7251,7 +7327,7 @@
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A62" s="47"/>
+      <c r="A62" s="50"/>
       <c r="B62" s="3" t="s">
         <v>66</v>
       </c>
@@ -7329,7 +7405,7 @@
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A63" s="47"/>
+      <c r="A63" s="50"/>
       <c r="B63" s="3" t="s">
         <v>67</v>
       </c>
@@ -7407,7 +7483,7 @@
       </c>
     </row>
     <row r="64" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="48"/>
+      <c r="A64" s="51"/>
       <c r="B64" s="33" t="s">
         <v>68</v>
       </c>
@@ -7485,7 +7561,7 @@
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A65" s="46" t="s">
+      <c r="A65" s="49" t="s">
         <v>69</v>
       </c>
       <c r="B65" s="32" t="s">
@@ -7565,7 +7641,7 @@
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A66" s="47"/>
+      <c r="A66" s="50"/>
       <c r="B66" s="3" t="s">
         <v>71</v>
       </c>
@@ -7643,7 +7719,7 @@
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A67" s="47"/>
+      <c r="A67" s="50"/>
       <c r="B67" s="3" t="s">
         <v>64</v>
       </c>
@@ -7721,7 +7797,7 @@
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A68" s="47"/>
+      <c r="A68" s="50"/>
       <c r="B68" s="3" t="s">
         <v>72</v>
       </c>
@@ -7799,7 +7875,7 @@
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A69" s="47"/>
+      <c r="A69" s="50"/>
       <c r="B69" s="3" t="s">
         <v>73</v>
       </c>
@@ -7877,7 +7953,7 @@
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
+      <c r="A70" s="50"/>
       <c r="B70" s="3" t="s">
         <v>62</v>
       </c>
@@ -7955,7 +8031,7 @@
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
+      <c r="A71" s="50"/>
       <c r="B71" s="3" t="s">
         <v>65</v>
       </c>
@@ -8033,7 +8109,7 @@
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A72" s="47"/>
+      <c r="A72" s="50"/>
       <c r="B72" s="3" t="s">
         <v>66</v>
       </c>
@@ -8111,7 +8187,7 @@
       </c>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A73" s="47"/>
+      <c r="A73" s="50"/>
       <c r="B73" s="3" t="s">
         <v>74</v>
       </c>
@@ -8189,7 +8265,7 @@
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A74" s="47"/>
+      <c r="A74" s="50"/>
       <c r="B74" s="3" t="s">
         <v>75</v>
       </c>
@@ -8267,7 +8343,7 @@
       </c>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A75" s="47"/>
+      <c r="A75" s="50"/>
       <c r="B75" s="3" t="s">
         <v>68</v>
       </c>
@@ -8345,7 +8421,7 @@
       </c>
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
+      <c r="A76" s="50"/>
       <c r="B76" s="3" t="s">
         <v>76</v>
       </c>
@@ -8423,7 +8499,7 @@
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A77" s="47"/>
+      <c r="A77" s="50"/>
       <c r="B77" s="3" t="s">
         <v>77</v>
       </c>
@@ -8501,7 +8577,7 @@
       </c>
     </row>
     <row r="78" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48"/>
+      <c r="A78" s="51"/>
       <c r="B78" s="33" t="s">
         <v>78</v>
       </c>
@@ -8579,7 +8655,7 @@
       </c>
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A79" s="46" t="s">
+      <c r="A79" s="49" t="s">
         <v>79</v>
       </c>
       <c r="B79" s="32" t="s">
@@ -8659,7 +8735,7 @@
       </c>
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A80" s="47"/>
+      <c r="A80" s="50"/>
       <c r="B80" s="3" t="s">
         <v>81</v>
       </c>
@@ -8737,7 +8813,7 @@
       </c>
     </row>
     <row r="81" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A81" s="47"/>
+      <c r="A81" s="50"/>
       <c r="B81" s="3" t="s">
         <v>82</v>
       </c>
@@ -8815,7 +8891,7 @@
       </c>
     </row>
     <row r="82" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A82" s="47"/>
+      <c r="A82" s="50"/>
       <c r="B82" s="3" t="s">
         <v>83</v>
       </c>
@@ -8893,7 +8969,7 @@
       </c>
     </row>
     <row r="83" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A83" s="47"/>
+      <c r="A83" s="50"/>
       <c r="B83" s="3" t="s">
         <v>84</v>
       </c>
@@ -8971,7 +9047,7 @@
       </c>
     </row>
     <row r="84" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A84" s="47"/>
+      <c r="A84" s="50"/>
       <c r="B84" s="3" t="s">
         <v>85</v>
       </c>
@@ -9049,7 +9125,7 @@
       </c>
     </row>
     <row r="85" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A85" s="47"/>
+      <c r="A85" s="50"/>
       <c r="B85" s="3" t="s">
         <v>86</v>
       </c>
@@ -9127,7 +9203,7 @@
       </c>
     </row>
     <row r="86" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A86" s="47"/>
+      <c r="A86" s="50"/>
       <c r="B86" s="3" t="s">
         <v>87</v>
       </c>
@@ -9205,7 +9281,7 @@
       </c>
     </row>
     <row r="87" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A87" s="47"/>
+      <c r="A87" s="50"/>
       <c r="B87" s="3" t="s">
         <v>88</v>
       </c>
@@ -9283,7 +9359,7 @@
       </c>
     </row>
     <row r="88" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A88" s="47"/>
+      <c r="A88" s="50"/>
       <c r="B88" s="3" t="s">
         <v>89</v>
       </c>
@@ -9361,7 +9437,7 @@
       </c>
     </row>
     <row r="89" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A89" s="47"/>
+      <c r="A89" s="50"/>
       <c r="B89" s="3" t="s">
         <v>90</v>
       </c>
@@ -9439,7 +9515,7 @@
       </c>
     </row>
     <row r="90" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A90" s="47"/>
+      <c r="A90" s="50"/>
       <c r="B90" s="3" t="s">
         <v>62</v>
       </c>
@@ -9517,7 +9593,7 @@
       </c>
     </row>
     <row r="91" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A91" s="47"/>
+      <c r="A91" s="50"/>
       <c r="B91" s="3" t="s">
         <v>91</v>
       </c>
@@ -9595,7 +9671,7 @@
       </c>
     </row>
     <row r="92" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A92" s="47"/>
+      <c r="A92" s="50"/>
       <c r="B92" s="3" t="s">
         <v>92</v>
       </c>
@@ -9673,7 +9749,7 @@
       </c>
     </row>
     <row r="93" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A93" s="47"/>
+      <c r="A93" s="50"/>
       <c r="B93" s="3" t="s">
         <v>93</v>
       </c>
@@ -9751,7 +9827,7 @@
       </c>
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A94" s="47"/>
+      <c r="A94" s="50"/>
       <c r="B94" s="3" t="s">
         <v>94</v>
       </c>
@@ -9829,7 +9905,7 @@
       </c>
     </row>
     <row r="95" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A95" s="47"/>
+      <c r="A95" s="50"/>
       <c r="B95" s="3" t="s">
         <v>95</v>
       </c>
@@ -9907,7 +9983,7 @@
       </c>
     </row>
     <row r="96" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A96" s="47"/>
+      <c r="A96" s="50"/>
       <c r="B96" s="3" t="s">
         <v>96</v>
       </c>
@@ -9985,7 +10061,7 @@
       </c>
     </row>
     <row r="97" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A97" s="47"/>
+      <c r="A97" s="50"/>
       <c r="B97" s="3" t="s">
         <v>78</v>
       </c>
@@ -10063,7 +10139,7 @@
       </c>
     </row>
     <row r="98" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A98" s="47"/>
+      <c r="A98" s="50"/>
       <c r="B98" s="3" t="s">
         <v>97</v>
       </c>
@@ -10141,7 +10217,7 @@
       </c>
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A99" s="47"/>
+      <c r="A99" s="50"/>
       <c r="B99" s="3" t="s">
         <v>98</v>
       </c>
@@ -10219,7 +10295,7 @@
       </c>
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
+      <c r="A100" s="50"/>
       <c r="B100" s="3" t="s">
         <v>99</v>
       </c>
@@ -10297,7 +10373,7 @@
       </c>
     </row>
     <row r="101" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
+      <c r="A101" s="50"/>
       <c r="B101" s="3" t="s">
         <v>100</v>
       </c>
@@ -10375,7 +10451,7 @@
       </c>
     </row>
     <row r="102" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A102" s="47"/>
+      <c r="A102" s="50"/>
       <c r="B102" s="3" t="s">
         <v>101</v>
       </c>
@@ -10453,7 +10529,7 @@
       </c>
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A103" s="47"/>
+      <c r="A103" s="50"/>
       <c r="B103" s="3" t="s">
         <v>102</v>
       </c>
@@ -10531,7 +10607,7 @@
       </c>
     </row>
     <row r="104" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="48"/>
+      <c r="A104" s="51"/>
       <c r="B104" s="33" t="s">
         <v>103</v>
       </c>
@@ -10644,7 +10720,7 @@
       <c r="Z106" s="55"/>
     </row>
     <row r="107" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A107" s="46" t="s">
+      <c r="A107" s="49" t="s">
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
@@ -10724,7 +10800,7 @@
       </c>
     </row>
     <row r="108" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A108" s="47"/>
+      <c r="A108" s="50"/>
       <c r="B108" s="4" t="s">
         <v>107</v>
       </c>
@@ -10802,7 +10878,7 @@
       </c>
     </row>
     <row r="109" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A109" s="47"/>
+      <c r="A109" s="50"/>
       <c r="B109" s="4" t="s">
         <v>108</v>
       </c>
@@ -10880,7 +10956,7 @@
       </c>
     </row>
     <row r="110" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A110" s="47"/>
+      <c r="A110" s="50"/>
       <c r="B110" s="4" t="s">
         <v>109</v>
       </c>
@@ -10958,7 +11034,7 @@
       </c>
     </row>
     <row r="111" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A111" s="47"/>
+      <c r="A111" s="50"/>
       <c r="B111" s="4" t="s">
         <v>110</v>
       </c>
@@ -11036,7 +11112,7 @@
       </c>
     </row>
     <row r="112" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A112" s="47"/>
+      <c r="A112" s="50"/>
       <c r="B112" s="4" t="s">
         <v>111</v>
       </c>
@@ -11114,7 +11190,7 @@
       </c>
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A113" s="47"/>
+      <c r="A113" s="50"/>
       <c r="B113" s="4" t="s">
         <v>112</v>
       </c>
@@ -11192,7 +11268,7 @@
       </c>
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A114" s="47"/>
+      <c r="A114" s="50"/>
       <c r="B114" s="4" t="s">
         <v>5</v>
       </c>
@@ -11270,7 +11346,7 @@
       </c>
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A115" s="47"/>
+      <c r="A115" s="50"/>
       <c r="B115" s="4" t="s">
         <v>113</v>
       </c>
@@ -11348,7 +11424,7 @@
       </c>
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A116" s="47"/>
+      <c r="A116" s="50"/>
       <c r="B116" s="4" t="s">
         <v>114</v>
       </c>
@@ -11426,7 +11502,7 @@
       </c>
     </row>
     <row r="117" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A117" s="47"/>
+      <c r="A117" s="50"/>
       <c r="B117" s="4" t="s">
         <v>115</v>
       </c>
@@ -11504,7 +11580,7 @@
       </c>
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A118" s="47"/>
+      <c r="A118" s="50"/>
       <c r="B118" s="4" t="s">
         <v>116</v>
       </c>
@@ -11582,7 +11658,7 @@
       </c>
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A119" s="47"/>
+      <c r="A119" s="50"/>
       <c r="B119" s="4" t="s">
         <v>117</v>
       </c>
@@ -11660,7 +11736,7 @@
       </c>
     </row>
     <row r="120" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A120" s="47"/>
+      <c r="A120" s="50"/>
       <c r="B120" s="4" t="s">
         <v>118</v>
       </c>
@@ -11738,7 +11814,7 @@
       </c>
     </row>
     <row r="121" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="48"/>
+      <c r="A121" s="51"/>
       <c r="B121" s="37" t="s">
         <v>119</v>
       </c>
@@ -11816,7 +11892,7 @@
       </c>
     </row>
     <row r="122" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A122" s="46" t="s">
+      <c r="A122" s="49" t="s">
         <v>120</v>
       </c>
       <c r="B122" s="36" t="s">
@@ -11896,7 +11972,7 @@
       </c>
     </row>
     <row r="123" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A123" s="47"/>
+      <c r="A123" s="50"/>
       <c r="B123" s="4" t="s">
         <v>122</v>
       </c>
@@ -11974,7 +12050,7 @@
       </c>
     </row>
     <row r="124" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A124" s="47"/>
+      <c r="A124" s="50"/>
       <c r="B124" s="4" t="s">
         <v>123</v>
       </c>
@@ -12052,7 +12128,7 @@
       </c>
     </row>
     <row r="125" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A125" s="47"/>
+      <c r="A125" s="50"/>
       <c r="B125" s="4" t="s">
         <v>124</v>
       </c>
@@ -12130,7 +12206,7 @@
       </c>
     </row>
     <row r="126" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A126" s="47"/>
+      <c r="A126" s="50"/>
       <c r="B126" s="4" t="s">
         <v>125</v>
       </c>
@@ -12208,7 +12284,7 @@
       </c>
     </row>
     <row r="127" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A127" s="47"/>
+      <c r="A127" s="50"/>
       <c r="B127" s="4" t="s">
         <v>126</v>
       </c>
@@ -12286,7 +12362,7 @@
       </c>
     </row>
     <row r="128" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A128" s="47"/>
+      <c r="A128" s="50"/>
       <c r="B128" s="4" t="s">
         <v>127</v>
       </c>
@@ -12364,7 +12440,7 @@
       </c>
     </row>
     <row r="129" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A129" s="47"/>
+      <c r="A129" s="50"/>
       <c r="B129" s="4" t="s">
         <v>128</v>
       </c>
@@ -12442,7 +12518,7 @@
       </c>
     </row>
     <row r="130" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A130" s="47"/>
+      <c r="A130" s="50"/>
       <c r="B130" s="4" t="s">
         <v>129</v>
       </c>
@@ -12520,7 +12596,7 @@
       </c>
     </row>
     <row r="131" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A131" s="47"/>
+      <c r="A131" s="50"/>
       <c r="B131" s="4" t="s">
         <v>130</v>
       </c>
@@ -12598,7 +12674,7 @@
       </c>
     </row>
     <row r="132" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A132" s="47"/>
+      <c r="A132" s="50"/>
       <c r="B132" s="4" t="s">
         <v>131</v>
       </c>
@@ -12676,7 +12752,7 @@
       </c>
     </row>
     <row r="133" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A133" s="47"/>
+      <c r="A133" s="50"/>
       <c r="B133" s="4" t="s">
         <v>132</v>
       </c>
@@ -12754,7 +12830,7 @@
       </c>
     </row>
     <row r="134" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A134" s="47"/>
+      <c r="A134" s="50"/>
       <c r="B134" s="4" t="s">
         <v>133</v>
       </c>
@@ -12832,7 +12908,7 @@
       </c>
     </row>
     <row r="135" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A135" s="47"/>
+      <c r="A135" s="50"/>
       <c r="B135" s="4" t="s">
         <v>134</v>
       </c>
@@ -12910,7 +12986,7 @@
       </c>
     </row>
     <row r="136" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A136" s="47"/>
+      <c r="A136" s="50"/>
       <c r="B136" s="4" t="s">
         <v>135</v>
       </c>
@@ -12988,7 +13064,7 @@
       </c>
     </row>
     <row r="137" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A137" s="47"/>
+      <c r="A137" s="50"/>
       <c r="B137" s="4" t="s">
         <v>136</v>
       </c>
@@ -13066,7 +13142,7 @@
       </c>
     </row>
     <row r="138" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A138" s="47"/>
+      <c r="A138" s="50"/>
       <c r="B138" s="4" t="s">
         <v>137</v>
       </c>
@@ -13144,7 +13220,7 @@
       </c>
     </row>
     <row r="139" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A139" s="47"/>
+      <c r="A139" s="50"/>
       <c r="B139" s="4" t="s">
         <v>138</v>
       </c>
@@ -13222,7 +13298,7 @@
       </c>
     </row>
     <row r="140" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A140" s="47"/>
+      <c r="A140" s="50"/>
       <c r="B140" s="4" t="s">
         <v>139</v>
       </c>
@@ -13300,7 +13376,7 @@
       </c>
     </row>
     <row r="141" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="48"/>
+      <c r="A141" s="51"/>
       <c r="B141" s="37" t="s">
         <v>140</v>
       </c>
@@ -13413,7 +13489,7 @@
       <c r="Z143" s="55"/>
     </row>
     <row r="144" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A144" s="46" t="s">
+      <c r="A144" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -13493,7 +13569,7 @@
       </c>
     </row>
     <row r="145" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A145" s="47"/>
+      <c r="A145" s="50"/>
       <c r="B145" s="5" t="s">
         <v>144</v>
       </c>
@@ -13571,7 +13647,7 @@
       </c>
     </row>
     <row r="146" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A146" s="47"/>
+      <c r="A146" s="50"/>
       <c r="B146" s="5" t="s">
         <v>145</v>
       </c>
@@ -13649,7 +13725,7 @@
       </c>
     </row>
     <row r="147" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A147" s="47"/>
+      <c r="A147" s="50"/>
       <c r="B147" s="5" t="s">
         <v>146</v>
       </c>
@@ -13727,7 +13803,7 @@
       </c>
     </row>
     <row r="148" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A148" s="47"/>
+      <c r="A148" s="50"/>
       <c r="B148" s="5" t="s">
         <v>147</v>
       </c>
@@ -13805,7 +13881,7 @@
       </c>
     </row>
     <row r="149" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A149" s="47"/>
+      <c r="A149" s="50"/>
       <c r="B149" s="5" t="s">
         <v>148</v>
       </c>
@@ -13883,7 +13959,7 @@
       </c>
     </row>
     <row r="150" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="48"/>
+      <c r="A150" s="51"/>
       <c r="B150" s="39" t="s">
         <v>149</v>
       </c>
@@ -13961,7 +14037,7 @@
       </c>
     </row>
     <row r="151" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A151" s="46" t="s">
+      <c r="A151" s="49" t="s">
         <v>150</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -14041,7 +14117,7 @@
       </c>
     </row>
     <row r="152" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A152" s="47"/>
+      <c r="A152" s="50"/>
       <c r="B152" s="5" t="s">
         <v>21</v>
       </c>
@@ -14119,7 +14195,7 @@
       </c>
     </row>
     <row r="153" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A153" s="47"/>
+      <c r="A153" s="50"/>
       <c r="B153" s="5" t="s">
         <v>152</v>
       </c>
@@ -14197,7 +14273,7 @@
       </c>
     </row>
     <row r="154" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A154" s="47"/>
+      <c r="A154" s="50"/>
       <c r="B154" s="5" t="s">
         <v>153</v>
       </c>
@@ -14275,7 +14351,7 @@
       </c>
     </row>
     <row r="155" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A155" s="47"/>
+      <c r="A155" s="50"/>
       <c r="B155" s="5" t="s">
         <v>154</v>
       </c>
@@ -14353,7 +14429,7 @@
       </c>
     </row>
     <row r="156" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A156" s="47"/>
+      <c r="A156" s="50"/>
       <c r="B156" s="5" t="s">
         <v>155</v>
       </c>
@@ -14431,7 +14507,7 @@
       </c>
     </row>
     <row r="157" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A157" s="47"/>
+      <c r="A157" s="50"/>
       <c r="B157" s="5" t="s">
         <v>156</v>
       </c>
@@ -14509,7 +14585,7 @@
       </c>
     </row>
     <row r="158" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A158" s="47"/>
+      <c r="A158" s="50"/>
       <c r="B158" s="5" t="s">
         <v>157</v>
       </c>
@@ -14587,7 +14663,7 @@
       </c>
     </row>
     <row r="159" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A159" s="47"/>
+      <c r="A159" s="50"/>
       <c r="B159" s="5" t="s">
         <v>158</v>
       </c>
@@ -14665,7 +14741,7 @@
       </c>
     </row>
     <row r="160" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A160" s="47"/>
+      <c r="A160" s="50"/>
       <c r="B160" s="5" t="s">
         <v>159</v>
       </c>
@@ -14743,7 +14819,7 @@
       </c>
     </row>
     <row r="161" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A161" s="47"/>
+      <c r="A161" s="50"/>
       <c r="B161" s="5" t="s">
         <v>160</v>
       </c>
@@ -14821,7 +14897,7 @@
       </c>
     </row>
     <row r="162" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A162" s="47"/>
+      <c r="A162" s="50"/>
       <c r="B162" s="5" t="s">
         <v>161</v>
       </c>
@@ -14899,7 +14975,7 @@
       </c>
     </row>
     <row r="163" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A163" s="47"/>
+      <c r="A163" s="50"/>
       <c r="B163" s="5" t="s">
         <v>162</v>
       </c>
@@ -14977,7 +15053,7 @@
       </c>
     </row>
     <row r="164" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A164" s="47"/>
+      <c r="A164" s="50"/>
       <c r="B164" s="5" t="s">
         <v>163</v>
       </c>
@@ -15055,7 +15131,7 @@
       </c>
     </row>
     <row r="165" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A165" s="47"/>
+      <c r="A165" s="50"/>
       <c r="B165" s="5" t="s">
         <v>164</v>
       </c>
@@ -15133,7 +15209,7 @@
       </c>
     </row>
     <row r="166" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A166" s="47"/>
+      <c r="A166" s="50"/>
       <c r="B166" s="5" t="s">
         <v>165</v>
       </c>
@@ -15211,7 +15287,7 @@
       </c>
     </row>
     <row r="167" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A167" s="47"/>
+      <c r="A167" s="50"/>
       <c r="B167" s="5" t="s">
         <v>166</v>
       </c>
@@ -15289,7 +15365,7 @@
       </c>
     </row>
     <row r="168" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A168" s="47"/>
+      <c r="A168" s="50"/>
       <c r="B168" s="5" t="s">
         <v>167</v>
       </c>
@@ -15367,7 +15443,7 @@
       </c>
     </row>
     <row r="169" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A169" s="47"/>
+      <c r="A169" s="50"/>
       <c r="B169" s="5" t="s">
         <v>168</v>
       </c>
@@ -15445,7 +15521,7 @@
       </c>
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A170" s="47"/>
+      <c r="A170" s="50"/>
       <c r="B170" s="5" t="s">
         <v>169</v>
       </c>
@@ -15523,7 +15599,7 @@
       </c>
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A171" s="47"/>
+      <c r="A171" s="50"/>
       <c r="B171" s="5" t="s">
         <v>170</v>
       </c>
@@ -15601,7 +15677,7 @@
       </c>
     </row>
     <row r="172" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="48"/>
+      <c r="A172" s="51"/>
       <c r="B172" s="39" t="s">
         <v>171</v>
       </c>
@@ -15714,7 +15790,7 @@
       <c r="Z174" s="55"/>
     </row>
     <row r="175" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A175" s="46" t="s">
+      <c r="A175" s="49" t="s">
         <v>173</v>
       </c>
       <c r="B175" s="40" t="s">
@@ -15794,7 +15870,7 @@
       </c>
     </row>
     <row r="176" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A176" s="47"/>
+      <c r="A176" s="50"/>
       <c r="B176" s="6" t="s">
         <v>175</v>
       </c>
@@ -15872,7 +15948,7 @@
       </c>
     </row>
     <row r="177" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A177" s="47"/>
+      <c r="A177" s="50"/>
       <c r="B177" s="6" t="s">
         <v>176</v>
       </c>
@@ -15950,7 +16026,7 @@
       </c>
     </row>
     <row r="178" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A178" s="47"/>
+      <c r="A178" s="50"/>
       <c r="B178" s="6" t="s">
         <v>177</v>
       </c>
@@ -16028,7 +16104,7 @@
       </c>
     </row>
     <row r="179" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A179" s="47"/>
+      <c r="A179" s="50"/>
       <c r="B179" s="6" t="s">
         <v>178</v>
       </c>
@@ -16106,7 +16182,7 @@
       </c>
     </row>
     <row r="180" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A180" s="47"/>
+      <c r="A180" s="50"/>
       <c r="B180" s="6" t="s">
         <v>124</v>
       </c>
@@ -16184,7 +16260,7 @@
       </c>
     </row>
     <row r="181" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A181" s="47"/>
+      <c r="A181" s="50"/>
       <c r="B181" s="6" t="s">
         <v>179</v>
       </c>
@@ -16262,7 +16338,7 @@
       </c>
     </row>
     <row r="182" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A182" s="47"/>
+      <c r="A182" s="50"/>
       <c r="B182" s="6" t="s">
         <v>180</v>
       </c>
@@ -16340,7 +16416,7 @@
       </c>
     </row>
     <row r="183" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A183" s="47"/>
+      <c r="A183" s="50"/>
       <c r="B183" s="6" t="s">
         <v>181</v>
       </c>
@@ -16418,7 +16494,7 @@
       </c>
     </row>
     <row r="184" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A184" s="47"/>
+      <c r="A184" s="50"/>
       <c r="B184" s="6" t="s">
         <v>182</v>
       </c>
@@ -16496,7 +16572,7 @@
       </c>
     </row>
     <row r="185" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A185" s="47"/>
+      <c r="A185" s="50"/>
       <c r="B185" s="6" t="s">
         <v>183</v>
       </c>
@@ -16574,7 +16650,7 @@
       </c>
     </row>
     <row r="186" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A186" s="47"/>
+      <c r="A186" s="50"/>
       <c r="B186" s="6" t="s">
         <v>184</v>
       </c>
@@ -16652,7 +16728,7 @@
       </c>
     </row>
     <row r="187" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A187" s="47"/>
+      <c r="A187" s="50"/>
       <c r="B187" s="6" t="s">
         <v>135</v>
       </c>
@@ -16730,7 +16806,7 @@
       </c>
     </row>
     <row r="188" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A188" s="47"/>
+      <c r="A188" s="50"/>
       <c r="B188" s="6" t="s">
         <v>185</v>
       </c>
@@ -16808,7 +16884,7 @@
       </c>
     </row>
     <row r="189" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A189" s="47"/>
+      <c r="A189" s="50"/>
       <c r="B189" s="6" t="s">
         <v>186</v>
       </c>
@@ -16886,7 +16962,7 @@
       </c>
     </row>
     <row r="190" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A190" s="47"/>
+      <c r="A190" s="50"/>
       <c r="B190" s="6" t="s">
         <v>187</v>
       </c>
@@ -16964,7 +17040,7 @@
       </c>
     </row>
     <row r="191" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A191" s="47"/>
+      <c r="A191" s="50"/>
       <c r="B191" s="6" t="s">
         <v>188</v>
       </c>
@@ -17042,7 +17118,7 @@
       </c>
     </row>
     <row r="192" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="48"/>
+      <c r="A192" s="51"/>
       <c r="B192" s="41" t="s">
         <v>189</v>
       </c>
@@ -17120,7 +17196,7 @@
       </c>
     </row>
     <row r="193" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A193" s="46" t="s">
+      <c r="A193" s="49" t="s">
         <v>190</v>
       </c>
       <c r="B193" s="40" t="s">
@@ -17200,7 +17276,7 @@
       </c>
     </row>
     <row r="194" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A194" s="47"/>
+      <c r="A194" s="50"/>
       <c r="B194" s="6" t="s">
         <v>192</v>
       </c>
@@ -17278,7 +17354,7 @@
       </c>
     </row>
     <row r="195" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A195" s="47"/>
+      <c r="A195" s="50"/>
       <c r="B195" s="6" t="s">
         <v>13</v>
       </c>
@@ -17356,7 +17432,7 @@
       </c>
     </row>
     <row r="196" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A196" s="47"/>
+      <c r="A196" s="50"/>
       <c r="B196" s="6" t="s">
         <v>174</v>
       </c>
@@ -17434,7 +17510,7 @@
       </c>
     </row>
     <row r="197" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A197" s="47"/>
+      <c r="A197" s="50"/>
       <c r="B197" s="6" t="s">
         <v>175</v>
       </c>
@@ -17512,7 +17588,7 @@
       </c>
     </row>
     <row r="198" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A198" s="47"/>
+      <c r="A198" s="50"/>
       <c r="B198" s="6" t="s">
         <v>193</v>
       </c>
@@ -17590,7 +17666,7 @@
       </c>
     </row>
     <row r="199" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A199" s="47"/>
+      <c r="A199" s="50"/>
       <c r="B199" s="6" t="s">
         <v>194</v>
       </c>
@@ -17668,7 +17744,7 @@
       </c>
     </row>
     <row r="200" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A200" s="47"/>
+      <c r="A200" s="50"/>
       <c r="B200" s="6" t="s">
         <v>195</v>
       </c>
@@ -17746,7 +17822,7 @@
       </c>
     </row>
     <row r="201" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A201" s="47"/>
+      <c r="A201" s="50"/>
       <c r="B201" s="6" t="s">
         <v>196</v>
       </c>
@@ -17824,7 +17900,7 @@
       </c>
     </row>
     <row r="202" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A202" s="47"/>
+      <c r="A202" s="50"/>
       <c r="B202" s="6" t="s">
         <v>197</v>
       </c>
@@ -17902,7 +17978,7 @@
       </c>
     </row>
     <row r="203" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A203" s="47"/>
+      <c r="A203" s="50"/>
       <c r="B203" s="6" t="s">
         <v>198</v>
       </c>
@@ -17980,7 +18056,7 @@
       </c>
     </row>
     <row r="204" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A204" s="47"/>
+      <c r="A204" s="50"/>
       <c r="B204" s="6" t="s">
         <v>199</v>
       </c>
@@ -18058,7 +18134,7 @@
       </c>
     </row>
     <row r="205" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A205" s="47"/>
+      <c r="A205" s="50"/>
       <c r="B205" s="6" t="s">
         <v>200</v>
       </c>
@@ -18136,7 +18212,7 @@
       </c>
     </row>
     <row r="206" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A206" s="47"/>
+      <c r="A206" s="50"/>
       <c r="B206" s="6" t="s">
         <v>201</v>
       </c>
@@ -18214,7 +18290,7 @@
       </c>
     </row>
     <row r="207" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A207" s="47"/>
+      <c r="A207" s="50"/>
       <c r="B207" s="6" t="s">
         <v>202</v>
       </c>
@@ -18292,7 +18368,7 @@
       </c>
     </row>
     <row r="208" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A208" s="47"/>
+      <c r="A208" s="50"/>
       <c r="B208" s="6" t="s">
         <v>203</v>
       </c>
@@ -18370,7 +18446,7 @@
       </c>
     </row>
     <row r="209" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A209" s="47"/>
+      <c r="A209" s="50"/>
       <c r="B209" s="6" t="s">
         <v>204</v>
       </c>
@@ -18448,7 +18524,7 @@
       </c>
     </row>
     <row r="210" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A210" s="47"/>
+      <c r="A210" s="50"/>
       <c r="B210" s="6" t="s">
         <v>205</v>
       </c>
@@ -18526,7 +18602,7 @@
       </c>
     </row>
     <row r="211" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A211" s="47"/>
+      <c r="A211" s="50"/>
       <c r="B211" s="6" t="s">
         <v>206</v>
       </c>
@@ -18604,7 +18680,7 @@
       </c>
     </row>
     <row r="212" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A212" s="47"/>
+      <c r="A212" s="50"/>
       <c r="B212" s="6" t="s">
         <v>207</v>
       </c>
@@ -18682,7 +18758,7 @@
       </c>
     </row>
     <row r="213" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A213" s="47"/>
+      <c r="A213" s="50"/>
       <c r="B213" s="6" t="s">
         <v>208</v>
       </c>
@@ -18760,7 +18836,7 @@
       </c>
     </row>
     <row r="214" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A214" s="47"/>
+      <c r="A214" s="50"/>
       <c r="B214" s="6" t="s">
         <v>209</v>
       </c>
@@ -18838,7 +18914,7 @@
       </c>
     </row>
     <row r="215" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A215" s="47"/>
+      <c r="A215" s="50"/>
       <c r="B215" s="6" t="s">
         <v>210</v>
       </c>
@@ -18916,7 +18992,7 @@
       </c>
     </row>
     <row r="216" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="48"/>
+      <c r="A216" s="51"/>
       <c r="B216" s="41" t="s">
         <v>211</v>
       </c>
@@ -18994,7 +19070,7 @@
       </c>
     </row>
     <row r="217" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A217" s="46" t="s">
+      <c r="A217" s="49" t="s">
         <v>212</v>
       </c>
       <c r="B217" s="40" t="s">
@@ -19074,7 +19150,7 @@
       </c>
     </row>
     <row r="218" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A218" s="47"/>
+      <c r="A218" s="50"/>
       <c r="B218" s="6" t="s">
         <v>175</v>
       </c>
@@ -19152,7 +19228,7 @@
       </c>
     </row>
     <row r="219" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A219" s="47"/>
+      <c r="A219" s="50"/>
       <c r="B219" s="6" t="s">
         <v>176</v>
       </c>
@@ -19230,7 +19306,7 @@
       </c>
     </row>
     <row r="220" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A220" s="47"/>
+      <c r="A220" s="50"/>
       <c r="B220" s="6" t="s">
         <v>131</v>
       </c>
@@ -19308,7 +19384,7 @@
       </c>
     </row>
     <row r="221" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A221" s="47"/>
+      <c r="A221" s="50"/>
       <c r="B221" s="6" t="s">
         <v>213</v>
       </c>
@@ -19386,7 +19462,7 @@
       </c>
     </row>
     <row r="222" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A222" s="47"/>
+      <c r="A222" s="50"/>
       <c r="B222" s="6" t="s">
         <v>214</v>
       </c>
@@ -19464,7 +19540,7 @@
       </c>
     </row>
     <row r="223" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A223" s="47"/>
+      <c r="A223" s="50"/>
       <c r="B223" s="6" t="s">
         <v>215</v>
       </c>
@@ -19542,7 +19618,7 @@
       </c>
     </row>
     <row r="224" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A224" s="47"/>
+      <c r="A224" s="50"/>
       <c r="B224" s="6" t="s">
         <v>216</v>
       </c>
@@ -19620,7 +19696,7 @@
       </c>
     </row>
     <row r="225" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A225" s="47"/>
+      <c r="A225" s="50"/>
       <c r="B225" s="6" t="s">
         <v>217</v>
       </c>
@@ -19698,7 +19774,7 @@
       </c>
     </row>
     <row r="226" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A226" s="47"/>
+      <c r="A226" s="50"/>
       <c r="B226" s="6" t="s">
         <v>218</v>
       </c>
@@ -19776,7 +19852,7 @@
       </c>
     </row>
     <row r="227" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A227" s="47"/>
+      <c r="A227" s="50"/>
       <c r="B227" s="6" t="s">
         <v>219</v>
       </c>
@@ -19854,7 +19930,7 @@
       </c>
     </row>
     <row r="228" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A228" s="47"/>
+      <c r="A228" s="50"/>
       <c r="B228" s="6" t="s">
         <v>220</v>
       </c>
@@ -19932,7 +20008,7 @@
       </c>
     </row>
     <row r="229" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="48"/>
+      <c r="A229" s="51"/>
       <c r="B229" s="41" t="s">
         <v>221</v>
       </c>
@@ -20041,7 +20117,7 @@
       <c r="Z231" s="55"/>
     </row>
     <row r="232" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A232" s="46" t="s">
+      <c r="A232" s="49" t="s">
         <v>223</v>
       </c>
       <c r="B232" s="42" t="s">
@@ -20121,7 +20197,7 @@
       </c>
     </row>
     <row r="233" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A233" s="47"/>
+      <c r="A233" s="50"/>
       <c r="B233" s="7" t="s">
         <v>225</v>
       </c>
@@ -20199,7 +20275,7 @@
       </c>
     </row>
     <row r="234" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A234" s="47"/>
+      <c r="A234" s="50"/>
       <c r="B234" s="7" t="s">
         <v>121</v>
       </c>
@@ -20277,7 +20353,7 @@
       </c>
     </row>
     <row r="235" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A235" s="47"/>
+      <c r="A235" s="50"/>
       <c r="B235" s="7" t="s">
         <v>122</v>
       </c>
@@ -20355,7 +20431,7 @@
       </c>
     </row>
     <row r="236" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A236" s="47"/>
+      <c r="A236" s="50"/>
       <c r="B236" s="7" t="s">
         <v>226</v>
       </c>
@@ -20433,7 +20509,7 @@
       </c>
     </row>
     <row r="237" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A237" s="47"/>
+      <c r="A237" s="50"/>
       <c r="B237" s="7" t="s">
         <v>227</v>
       </c>
@@ -20511,7 +20587,7 @@
       </c>
     </row>
     <row r="238" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A238" s="47"/>
+      <c r="A238" s="50"/>
       <c r="B238" s="7" t="s">
         <v>228</v>
       </c>
@@ -20589,7 +20665,7 @@
       </c>
     </row>
     <row r="239" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A239" s="47"/>
+      <c r="A239" s="50"/>
       <c r="B239" s="7" t="s">
         <v>229</v>
       </c>
@@ -20667,7 +20743,7 @@
       </c>
     </row>
     <row r="240" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A240" s="47"/>
+      <c r="A240" s="50"/>
       <c r="B240" s="7" t="s">
         <v>230</v>
       </c>
@@ -20745,7 +20821,7 @@
       </c>
     </row>
     <row r="241" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A241" s="47"/>
+      <c r="A241" s="50"/>
       <c r="B241" s="7" t="s">
         <v>231</v>
       </c>
@@ -20823,7 +20899,7 @@
       </c>
     </row>
     <row r="242" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A242" s="47"/>
+      <c r="A242" s="50"/>
       <c r="B242" s="7" t="s">
         <v>134</v>
       </c>
@@ -20901,7 +20977,7 @@
       </c>
     </row>
     <row r="243" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A243" s="47"/>
+      <c r="A243" s="50"/>
       <c r="B243" s="7" t="s">
         <v>232</v>
       </c>
@@ -20979,7 +21055,7 @@
       </c>
     </row>
     <row r="244" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A244" s="47"/>
+      <c r="A244" s="50"/>
       <c r="B244" s="7" t="s">
         <v>198</v>
       </c>
@@ -21057,7 +21133,7 @@
       </c>
     </row>
     <row r="245" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A245" s="47"/>
+      <c r="A245" s="50"/>
       <c r="B245" s="7" t="s">
         <v>233</v>
       </c>
@@ -21135,7 +21211,7 @@
       </c>
     </row>
     <row r="246" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A246" s="47"/>
+      <c r="A246" s="50"/>
       <c r="B246" s="7" t="s">
         <v>234</v>
       </c>
@@ -21213,7 +21289,7 @@
       </c>
     </row>
     <row r="247" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A247" s="47"/>
+      <c r="A247" s="50"/>
       <c r="B247" s="7" t="s">
         <v>235</v>
       </c>
@@ -21291,7 +21367,7 @@
       </c>
     </row>
     <row r="248" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A248" s="47"/>
+      <c r="A248" s="50"/>
       <c r="B248" s="7" t="s">
         <v>236</v>
       </c>
@@ -21369,7 +21445,7 @@
       </c>
     </row>
     <row r="249" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A249" s="47"/>
+      <c r="A249" s="50"/>
       <c r="B249" s="7" t="s">
         <v>237</v>
       </c>
@@ -21447,7 +21523,7 @@
       </c>
     </row>
     <row r="250" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A250" s="47"/>
+      <c r="A250" s="50"/>
       <c r="B250" s="7" t="s">
         <v>238</v>
       </c>
@@ -21525,7 +21601,7 @@
       </c>
     </row>
     <row r="251" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A251" s="47"/>
+      <c r="A251" s="50"/>
       <c r="B251" s="7" t="s">
         <v>239</v>
       </c>
@@ -21603,7 +21679,7 @@
       </c>
     </row>
     <row r="252" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A252" s="47"/>
+      <c r="A252" s="50"/>
       <c r="B252" s="7" t="s">
         <v>240</v>
       </c>
@@ -21681,7 +21757,7 @@
       </c>
     </row>
     <row r="253" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A253" s="47"/>
+      <c r="A253" s="50"/>
       <c r="B253" s="7" t="s">
         <v>241</v>
       </c>
@@ -21759,7 +21835,7 @@
       </c>
     </row>
     <row r="254" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A254" s="47"/>
+      <c r="A254" s="50"/>
       <c r="B254" s="7" t="s">
         <v>242</v>
       </c>
@@ -21837,7 +21913,7 @@
       </c>
     </row>
     <row r="255" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A255" s="47"/>
+      <c r="A255" s="50"/>
       <c r="B255" s="7" t="s">
         <v>243</v>
       </c>
@@ -21915,7 +21991,7 @@
       </c>
     </row>
     <row r="256" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A256" s="47"/>
+      <c r="A256" s="50"/>
       <c r="B256" s="7" t="s">
         <v>244</v>
       </c>
@@ -21993,7 +22069,7 @@
       </c>
     </row>
     <row r="257" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A257" s="47"/>
+      <c r="A257" s="50"/>
       <c r="B257" s="7" t="s">
         <v>245</v>
       </c>
@@ -22071,7 +22147,7 @@
       </c>
     </row>
     <row r="258" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A258" s="47"/>
+      <c r="A258" s="50"/>
       <c r="B258" s="7" t="s">
         <v>246</v>
       </c>
@@ -22149,7 +22225,7 @@
       </c>
     </row>
     <row r="259" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="48"/>
+      <c r="A259" s="51"/>
       <c r="B259" s="43" t="s">
         <v>247</v>
       </c>
@@ -22227,7 +22303,7 @@
       </c>
     </row>
     <row r="260" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A260" s="46" t="s">
+      <c r="A260" s="49" t="s">
         <v>248</v>
       </c>
       <c r="B260" s="42" t="s">
@@ -22307,7 +22383,7 @@
       </c>
     </row>
     <row r="261" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A261" s="47"/>
+      <c r="A261" s="50"/>
       <c r="B261" s="7" t="s">
         <v>250</v>
       </c>
@@ -22385,7 +22461,7 @@
       </c>
     </row>
     <row r="262" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A262" s="47"/>
+      <c r="A262" s="50"/>
       <c r="B262" s="7" t="s">
         <v>251</v>
       </c>
@@ -22463,7 +22539,7 @@
       </c>
     </row>
     <row r="263" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A263" s="47"/>
+      <c r="A263" s="50"/>
       <c r="B263" s="7" t="s">
         <v>252</v>
       </c>
@@ -22541,7 +22617,7 @@
       </c>
     </row>
     <row r="264" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A264" s="47"/>
+      <c r="A264" s="50"/>
       <c r="B264" s="7" t="s">
         <v>253</v>
       </c>
@@ -22619,7 +22695,7 @@
       </c>
     </row>
     <row r="265" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A265" s="47"/>
+      <c r="A265" s="50"/>
       <c r="B265" s="7" t="s">
         <v>254</v>
       </c>
@@ -22697,7 +22773,7 @@
       </c>
     </row>
     <row r="266" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A266" s="47"/>
+      <c r="A266" s="50"/>
       <c r="B266" s="7" t="s">
         <v>255</v>
       </c>
@@ -22775,7 +22851,7 @@
       </c>
     </row>
     <row r="267" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A267" s="47"/>
+      <c r="A267" s="50"/>
       <c r="B267" s="7" t="s">
         <v>256</v>
       </c>
@@ -22853,7 +22929,7 @@
       </c>
     </row>
     <row r="268" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A268" s="47"/>
+      <c r="A268" s="50"/>
       <c r="B268" s="7" t="s">
         <v>257</v>
       </c>
@@ -22931,7 +23007,7 @@
       </c>
     </row>
     <row r="269" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A269" s="47"/>
+      <c r="A269" s="50"/>
       <c r="B269" s="7" t="s">
         <v>258</v>
       </c>
@@ -23009,7 +23085,7 @@
       </c>
     </row>
     <row r="270" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A270" s="47"/>
+      <c r="A270" s="50"/>
       <c r="B270" s="7" t="s">
         <v>259</v>
       </c>
@@ -23087,7 +23163,7 @@
       </c>
     </row>
     <row r="271" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A271" s="47"/>
+      <c r="A271" s="50"/>
       <c r="B271" s="7" t="s">
         <v>260</v>
       </c>
@@ -23165,7 +23241,7 @@
       </c>
     </row>
     <row r="272" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A272" s="47"/>
+      <c r="A272" s="50"/>
       <c r="B272" s="7" t="s">
         <v>261</v>
       </c>
@@ -23243,7 +23319,7 @@
       </c>
     </row>
     <row r="273" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A273" s="47"/>
+      <c r="A273" s="50"/>
       <c r="B273" s="7" t="s">
         <v>262</v>
       </c>
@@ -23321,7 +23397,7 @@
       </c>
     </row>
     <row r="274" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A274" s="47"/>
+      <c r="A274" s="50"/>
       <c r="B274" s="7" t="s">
         <v>263</v>
       </c>
@@ -23399,7 +23475,7 @@
       </c>
     </row>
     <row r="275" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A275" s="47"/>
+      <c r="A275" s="50"/>
       <c r="B275" s="7" t="s">
         <v>264</v>
       </c>
@@ -23477,7 +23553,7 @@
       </c>
     </row>
     <row r="276" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="48"/>
+      <c r="A276" s="51"/>
       <c r="B276" s="43" t="s">
         <v>265</v>
       </c>
@@ -23556,6 +23632,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A260:A276"/>
+    <mergeCell ref="A175:A192"/>
+    <mergeCell ref="A217:A229"/>
+    <mergeCell ref="A232:A259"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A193:A216"/>
     <mergeCell ref="A2:Z2"/>
     <mergeCell ref="A65:A78"/>
     <mergeCell ref="A106:Z106"/>
@@ -23572,24 +23654,18 @@
     <mergeCell ref="A28:A37"/>
     <mergeCell ref="A143:Z143"/>
     <mergeCell ref="A48:Z48"/>
-    <mergeCell ref="A260:A276"/>
-    <mergeCell ref="A175:A192"/>
-    <mergeCell ref="A217:A229"/>
-    <mergeCell ref="A232:A259"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A193:A216"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:Z276">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>C3="Consolidado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="19" priority="3">
       <formula>C3="En proceso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="18" priority="4">
       <formula>C3="Proyección"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="5">
+    <cfRule type="expression" dxfId="17" priority="5">
       <formula>C3="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23628,7 +23704,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="62" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
@@ -23640,18 +23716,18 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>3</v>
@@ -23663,12 +23739,12 @@
         <v>4</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B6">
         <f>INDEX(CONSOLIDADO!$B$4:$B$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -23696,7 +23772,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B7">
         <f>INDEX(CONSOLIDADO!$C$4:$C$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -23808,7 +23884,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B11" s="15">
         <f>INDEX(CONSOLIDADO!$G$4:$G$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -24046,20 +24122,20 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="61" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="59"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -24235,7 +24311,7 @@
         <v>271</v>
       </c>
       <c r="B41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(NORMATIVOS!$C$17:$Z$17,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -24307,7 +24383,7 @@
         <v>271</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(NORMATIVOS!$C$23:$Z$23,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -24355,7 +24431,7 @@
         <v>271</v>
       </c>
       <c r="B51" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(NORMATIVOS!$C$27:$Z$27,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -24751,7 +24827,7 @@
         <v>52</v>
       </c>
       <c r="B84" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX(NORMATIVOS!$C$62:$Z$62,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -24871,7 +24947,7 @@
         <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX(NORMATIVOS!$C$72:$Z$72,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25003,7 +25079,7 @@
         <v>79</v>
       </c>
       <c r="B105" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX(NORMATIVOS!$C$83:$Z$83,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25027,7 +25103,7 @@
         <v>79</v>
       </c>
       <c r="B107" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX(NORMATIVOS!$C$85:$Z$85,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25303,7 +25379,7 @@
         <v>105</v>
       </c>
       <c r="B130" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX(NORMATIVOS!$C$110:$Z$110,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25375,7 +25451,7 @@
         <v>105</v>
       </c>
       <c r="B136" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX(NORMATIVOS!$C$116:$Z$116,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25459,7 +25535,7 @@
         <v>120</v>
       </c>
       <c r="B143" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX(NORMATIVOS!$C$123:$Z$123,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25531,7 +25607,7 @@
         <v>120</v>
       </c>
       <c r="B149" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX(NORMATIVOS!$C$129:$Z$129,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25579,7 +25655,7 @@
         <v>120</v>
       </c>
       <c r="B153" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX(NORMATIVOS!$C$133:$Z$133,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25591,7 +25667,7 @@
         <v>120</v>
       </c>
       <c r="B154" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX(NORMATIVOS!$C$134:$Z$134,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25699,7 +25775,7 @@
         <v>142</v>
       </c>
       <c r="B163" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX(NORMATIVOS!$C$145:$Z$145,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25711,7 +25787,7 @@
         <v>142</v>
       </c>
       <c r="B164" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX(NORMATIVOS!$C$146:$Z$146,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -25867,7 +25943,7 @@
         <v>150</v>
       </c>
       <c r="B177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX(NORMATIVOS!$C$159:$Z$159,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26047,7 +26123,7 @@
         <v>278</v>
       </c>
       <c r="B192" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX(NORMATIVOS!$C$176:$Z$176,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26059,7 +26135,7 @@
         <v>278</v>
       </c>
       <c r="B193" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX(NORMATIVOS!$C$177:$Z$177,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26299,7 +26375,7 @@
         <v>190</v>
       </c>
       <c r="B213" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX(NORMATIVOS!$C$197:$Z$197,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26395,7 +26471,7 @@
         <v>190</v>
       </c>
       <c r="B221" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C221" t="str">
         <f>INDEX(NORMATIVOS!$C$205:$Z$205,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26407,7 +26483,7 @@
         <v>190</v>
       </c>
       <c r="B222" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C222" t="str">
         <f>INDEX(NORMATIVOS!$C$206:$Z$206,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26467,7 +26543,7 @@
         <v>190</v>
       </c>
       <c r="B227" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C227" t="str">
         <f>INDEX(NORMATIVOS!$C$211:$Z$211,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26551,7 +26627,7 @@
         <v>212</v>
       </c>
       <c r="B234" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C234" t="str">
         <f>INDEX(NORMATIVOS!$C$218:$Z$218,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26563,7 +26639,7 @@
         <v>212</v>
       </c>
       <c r="B235" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C235" t="str">
         <f>INDEX(NORMATIVOS!$C$219:$Z$219,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26635,7 +26711,7 @@
         <v>212</v>
       </c>
       <c r="B241" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C241" t="str">
         <f>INDEX(NORMATIVOS!$C$225:$Z$225,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26683,7 +26759,7 @@
         <v>212</v>
       </c>
       <c r="B245" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C245" t="str">
         <f>INDEX(NORMATIVOS!$C$229:$Z$229,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -26731,7 +26807,7 @@
         <v>223</v>
       </c>
       <c r="B249" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C249" t="str">
         <f>INDEX(NORMATIVOS!$C$235:$Z$235,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -27031,7 +27107,7 @@
         <v>248</v>
       </c>
       <c r="B274" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C274" t="str">
         <f>INDEX(NORMATIVOS!$C$260:$Z$260,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -27055,7 +27131,7 @@
         <v>248</v>
       </c>
       <c r="B276" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C276" t="str">
         <f>INDEX(NORMATIVOS!$C$262:$Z$262,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -27091,7 +27167,7 @@
         <v>248</v>
       </c>
       <c r="B279" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C279" t="str">
         <f>INDEX(NORMATIVOS!$C$265:$Z$265,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -27127,7 +27203,7 @@
         <v>248</v>
       </c>
       <c r="B282" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C282" t="str">
         <f>INDEX(NORMATIVOS!$C$268:$Z$268,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -27236,16 +27312,16 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="C27:C290">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>C27="Consolidado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>C27="En proceso"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="14" priority="3">
       <formula>C27="Proyección"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="13" priority="4">
       <formula>C27="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27284,7 +27360,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="62" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
@@ -27296,22 +27372,22 @@
     </row>
     <row r="3" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B3" s="16">
         <f>COUNTA(CONSOLIDADO!A4:A5)</f>
         <v>2</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B4" s="17">
         <f>AVERAGE(CONSOLIDADO!G4:G5)</f>
@@ -27327,7 +27403,7 @@
     </row>
     <row r="5" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B5" s="16">
         <f>SUM(CONSOLIDADO!C4:C5)</f>
@@ -27343,7 +27419,7 @@
     </row>
     <row r="6" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B6" s="16">
         <f>SUM(CONSOLIDADO!D4:D5)</f>
@@ -27368,16 +27444,16 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="61" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B10" s="59"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -27540,7 +27616,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -27548,12 +27624,12 @@
     <col min="3" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="24" style="63" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="62" t="s">
-        <v>279</v>
+        <v>341</v>
       </c>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
@@ -27563,15 +27639,16 @@
       <c r="G1" s="59"/>
       <c r="H1" s="59"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>281</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>282</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>273</v>
@@ -27583,10 +27660,10 @@
         <v>269</v>
       </c>
       <c r="G3" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="H3" s="64" t="s">
         <v>283</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -27618,9 +27695,9 @@
         <f>IFERROR(C4/(B4-F4),0)</f>
         <v>0.43129770992366412</v>
       </c>
-      <c r="H4" s="12" t="str">
-        <f>IF(G4&gt;=0.8,"Alto avance",IF(G4&gt;=0.5,"Avance medio","Requiere seguimiento"))</f>
-        <v>Requiere seguimiento</v>
+      <c r="H4" s="65" t="str">
+        <f>IF(G4&gt;=0.8,"Alto avance",IF(G4&gt;=0.5,"Avance medio",IF(G4&gt;=0.3,"Avance inicial",IF(G4&gt;=0.1,"Base solida","Base inicial"))))</f>
+        <v>Avance inicial</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -27652,295 +27729,32 @@
         <f>IFERROR(C5/(B5-F5),0)</f>
         <v>0.41825095057034223</v>
       </c>
-      <c r="H5" s="12" t="str">
-        <f>IF(G5&gt;=0.8,"Alto avance",IF(G5&gt;=0.5,"Avance medio","Requiere seguimiento"))</f>
-        <v>Requiere seguimiento</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="12"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="12"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="12"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="12"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="12"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="12"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="12"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="12"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="12"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="12"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="12"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="12"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="12"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="12"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="12"/>
+      <c r="H5" s="65" t="str">
+        <f t="shared" ref="H5" si="0">IF(G5&gt;=0.8,"Alto avance",IF(G5&gt;=0.5,"Avance medio",IF(G5&gt;=0.3,"Avance inicial",IF(G5&gt;=0.1,"Base solida","Base inicial"))))</f>
+        <v>Avance inicial</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Alto avance">
+      <formula>NOT(ISERROR(SEARCH("Alto avance",H1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="Avance medio">
+      <formula>NOT(ISERROR(SEARCH("Avance medio",H1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="Avance inicial">
+      <formula>NOT(ISERROR(SEARCH("Avance inicial",H1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="Base solida">
+      <formula>NOT(ISERROR(SEARCH("Base solida",H1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="Base inicial">
+      <formula>NOT(ISERROR(SEARCH("Base inicial",H1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -27973,7 +27787,7 @@
         <v>268</v>
       </c>
       <c r="G1" s="45" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -27987,13 +27801,13 @@
         <v>270</v>
       </c>
       <c r="G2" s="45" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I2" s="45" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -28010,10 +27824,10 @@
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -28030,10 +27844,10 @@
         <v>273</v>
       </c>
       <c r="H4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -28050,10 +27864,10 @@
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -28064,10 +27878,10 @@
         <v>269</v>
       </c>
       <c r="H6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -28150,7 +27964,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="62" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
@@ -28162,7 +27976,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B3" t="str">
         <f>NORMATIVOS!C1</f>
@@ -28171,10 +27985,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>3</v>
@@ -28186,15 +28000,15 @@
         <v>4</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B6">
         <f>INDEX(CONSOLIDADO!$B$4:$B$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -28226,7 +28040,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B7">
         <f>INDEX(CONSOLIDADO!$C$4:$C$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -28354,7 +28168,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B11" s="15">
         <f>INDEX(CONSOLIDADO!$G$4:$G$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -28411,10 +28225,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D13" t="s">
         <v>105</v>
@@ -28674,26 +28488,26 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="61" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="59"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>291</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
@@ -28981,7 +28795,7 @@
         <v>271</v>
       </c>
       <c r="B41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(NORMATIVOS!$C$17:$Z$17,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -29101,7 +28915,7 @@
         <v>271</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(NORMATIVOS!$C$23:$Z$23,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -29181,7 +28995,7 @@
         <v>271</v>
       </c>
       <c r="B51" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(NORMATIVOS!$C$27:$Z$27,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -29841,7 +29655,7 @@
         <v>52</v>
       </c>
       <c r="B84" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX(NORMATIVOS!$C$62:$Z$62,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -30041,7 +29855,7 @@
         <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX(NORMATIVOS!$C$72:$Z$72,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -30261,7 +30075,7 @@
         <v>79</v>
       </c>
       <c r="B105" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX(NORMATIVOS!$C$83:$Z$83,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -30301,7 +30115,7 @@
         <v>79</v>
       </c>
       <c r="B107" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX(NORMATIVOS!$C$85:$Z$85,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -30761,7 +30575,7 @@
         <v>105</v>
       </c>
       <c r="B130" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX(NORMATIVOS!$C$110:$Z$110,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -30881,7 +30695,7 @@
         <v>105</v>
       </c>
       <c r="B136" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX(NORMATIVOS!$C$116:$Z$116,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -31021,7 +30835,7 @@
         <v>120</v>
       </c>
       <c r="B143" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX(NORMATIVOS!$C$123:$Z$123,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -31141,7 +30955,7 @@
         <v>120</v>
       </c>
       <c r="B149" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX(NORMATIVOS!$C$129:$Z$129,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -31221,7 +31035,7 @@
         <v>120</v>
       </c>
       <c r="B153" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX(NORMATIVOS!$C$133:$Z$133,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -31241,7 +31055,7 @@
         <v>120</v>
       </c>
       <c r="B154" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX(NORMATIVOS!$C$134:$Z$134,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -31421,7 +31235,7 @@
         <v>142</v>
       </c>
       <c r="B163" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX(NORMATIVOS!$C$145:$Z$145,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -31441,7 +31255,7 @@
         <v>142</v>
       </c>
       <c r="B164" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX(NORMATIVOS!$C$146:$Z$146,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -31701,7 +31515,7 @@
         <v>150</v>
       </c>
       <c r="B177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX(NORMATIVOS!$C$159:$Z$159,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32001,7 +31815,7 @@
         <v>278</v>
       </c>
       <c r="B192" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX(NORMATIVOS!$C$176:$Z$176,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32021,7 +31835,7 @@
         <v>278</v>
       </c>
       <c r="B193" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX(NORMATIVOS!$C$177:$Z$177,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32421,7 +32235,7 @@
         <v>190</v>
       </c>
       <c r="B213" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX(NORMATIVOS!$C$197:$Z$197,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32581,7 +32395,7 @@
         <v>190</v>
       </c>
       <c r="B221" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C221" t="str">
         <f>INDEX(NORMATIVOS!$C$205:$Z$205,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32601,7 +32415,7 @@
         <v>190</v>
       </c>
       <c r="B222" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C222" t="str">
         <f>INDEX(NORMATIVOS!$C$206:$Z$206,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32701,7 +32515,7 @@
         <v>190</v>
       </c>
       <c r="B227" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C227" t="str">
         <f>INDEX(NORMATIVOS!$C$211:$Z$211,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32841,7 +32655,7 @@
         <v>212</v>
       </c>
       <c r="B234" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C234" t="str">
         <f>INDEX(NORMATIVOS!$C$218:$Z$218,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32861,7 +32675,7 @@
         <v>212</v>
       </c>
       <c r="B235" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C235" t="str">
         <f>INDEX(NORMATIVOS!$C$219:$Z$219,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -32981,7 +32795,7 @@
         <v>212</v>
       </c>
       <c r="B241" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C241" t="str">
         <f>INDEX(NORMATIVOS!$C$225:$Z$225,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -33061,7 +32875,7 @@
         <v>212</v>
       </c>
       <c r="B245" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C245" t="str">
         <f>INDEX(NORMATIVOS!$C$229:$Z$229,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -33141,7 +32955,7 @@
         <v>223</v>
       </c>
       <c r="B249" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C249" t="str">
         <f>INDEX(NORMATIVOS!$C$235:$Z$235,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -33641,7 +33455,7 @@
         <v>248</v>
       </c>
       <c r="B274" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C274" t="str">
         <f>INDEX(NORMATIVOS!$C$260:$Z$260,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -33681,7 +33495,7 @@
         <v>248</v>
       </c>
       <c r="B276" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C276" t="str">
         <f>INDEX(NORMATIVOS!$C$262:$Z$262,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -33741,7 +33555,7 @@
         <v>248</v>
       </c>
       <c r="B279" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C279" t="str">
         <f>INDEX(NORMATIVOS!$C$265:$Z$265,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -33801,7 +33615,7 @@
         <v>248</v>
       </c>
       <c r="B282" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C282" t="str">
         <f>INDEX(NORMATIVOS!$C$268:$Z$268,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -34020,7 +33834,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="62" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
@@ -34032,7 +33846,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B3" t="str">
         <f>NORMATIVOS!D1</f>
@@ -34041,10 +33855,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>3</v>
@@ -34056,15 +33870,15 @@
         <v>4</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B6">
         <f>INDEX(CONSOLIDADO!$B$4:$B$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -34096,7 +33910,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B7">
         <f>INDEX(CONSOLIDADO!$C$4:$C$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -34224,7 +34038,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B11" s="15">
         <f>INDEX(CONSOLIDADO!$G$4:$G$5,MATCH($B$3,CONSOLIDADO!$A$4:$A$5,0))</f>
@@ -34281,10 +34095,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D13" t="s">
         <v>105</v>
@@ -34544,26 +34358,26 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="61" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="59"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>291</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
@@ -34851,7 +34665,7 @@
         <v>271</v>
       </c>
       <c r="B41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(NORMATIVOS!$C$17:$Z$17,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -34971,7 +34785,7 @@
         <v>271</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(NORMATIVOS!$C$23:$Z$23,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -35051,7 +34865,7 @@
         <v>271</v>
       </c>
       <c r="B51" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(NORMATIVOS!$C$27:$Z$27,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -35711,7 +35525,7 @@
         <v>52</v>
       </c>
       <c r="B84" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX(NORMATIVOS!$C$62:$Z$62,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -35911,7 +35725,7 @@
         <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C94" t="str">
         <f>INDEX(NORMATIVOS!$C$72:$Z$72,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -36131,7 +35945,7 @@
         <v>79</v>
       </c>
       <c r="B105" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C105" t="str">
         <f>INDEX(NORMATIVOS!$C$83:$Z$83,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -36171,7 +35985,7 @@
         <v>79</v>
       </c>
       <c r="B107" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX(NORMATIVOS!$C$85:$Z$85,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -36631,7 +36445,7 @@
         <v>105</v>
       </c>
       <c r="B130" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C130" t="str">
         <f>INDEX(NORMATIVOS!$C$110:$Z$110,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -36751,7 +36565,7 @@
         <v>105</v>
       </c>
       <c r="B136" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX(NORMATIVOS!$C$116:$Z$116,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -36891,7 +36705,7 @@
         <v>120</v>
       </c>
       <c r="B143" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX(NORMATIVOS!$C$123:$Z$123,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -37011,7 +36825,7 @@
         <v>120</v>
       </c>
       <c r="B149" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX(NORMATIVOS!$C$129:$Z$129,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -37091,7 +36905,7 @@
         <v>120</v>
       </c>
       <c r="B153" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX(NORMATIVOS!$C$133:$Z$133,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -37111,7 +36925,7 @@
         <v>120</v>
       </c>
       <c r="B154" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX(NORMATIVOS!$C$134:$Z$134,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -37291,7 +37105,7 @@
         <v>142</v>
       </c>
       <c r="B163" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX(NORMATIVOS!$C$145:$Z$145,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -37311,7 +37125,7 @@
         <v>142</v>
       </c>
       <c r="B164" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX(NORMATIVOS!$C$146:$Z$146,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -37571,7 +37385,7 @@
         <v>150</v>
       </c>
       <c r="B177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX(NORMATIVOS!$C$159:$Z$159,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -37871,7 +37685,7 @@
         <v>278</v>
       </c>
       <c r="B192" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX(NORMATIVOS!$C$176:$Z$176,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -37891,7 +37705,7 @@
         <v>278</v>
       </c>
       <c r="B193" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX(NORMATIVOS!$C$177:$Z$177,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -38291,7 +38105,7 @@
         <v>190</v>
       </c>
       <c r="B213" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX(NORMATIVOS!$C$197:$Z$197,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -38451,7 +38265,7 @@
         <v>190</v>
       </c>
       <c r="B221" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C221" t="str">
         <f>INDEX(NORMATIVOS!$C$205:$Z$205,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -38471,7 +38285,7 @@
         <v>190</v>
       </c>
       <c r="B222" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C222" t="str">
         <f>INDEX(NORMATIVOS!$C$206:$Z$206,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -38571,7 +38385,7 @@
         <v>190</v>
       </c>
       <c r="B227" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C227" t="str">
         <f>INDEX(NORMATIVOS!$C$211:$Z$211,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -38711,7 +38525,7 @@
         <v>212</v>
       </c>
       <c r="B234" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C234" t="str">
         <f>INDEX(NORMATIVOS!$C$218:$Z$218,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -38731,7 +38545,7 @@
         <v>212</v>
       </c>
       <c r="B235" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C235" t="str">
         <f>INDEX(NORMATIVOS!$C$219:$Z$219,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -38851,7 +38665,7 @@
         <v>212</v>
       </c>
       <c r="B241" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C241" t="str">
         <f>INDEX(NORMATIVOS!$C$225:$Z$225,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -38931,7 +38745,7 @@
         <v>212</v>
       </c>
       <c r="B245" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C245" t="str">
         <f>INDEX(NORMATIVOS!$C$229:$Z$229,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -39011,7 +38825,7 @@
         <v>223</v>
       </c>
       <c r="B249" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C249" t="str">
         <f>INDEX(NORMATIVOS!$C$235:$Z$235,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -39511,7 +39325,7 @@
         <v>248</v>
       </c>
       <c r="B274" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C274" t="str">
         <f>INDEX(NORMATIVOS!$C$260:$Z$260,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -39551,7 +39365,7 @@
         <v>248</v>
       </c>
       <c r="B276" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C276" t="str">
         <f>INDEX(NORMATIVOS!$C$262:$Z$262,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -39611,7 +39425,7 @@
         <v>248</v>
       </c>
       <c r="B279" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C279" t="str">
         <f>INDEX(NORMATIVOS!$C$265:$Z$265,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
@@ -39671,7 +39485,7 @@
         <v>248</v>
       </c>
       <c r="B282" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C282" t="str">
         <f>INDEX(NORMATIVOS!$C$268:$Z$268,1,MATCH($B$3,NORMATIVOS!$C$1:$Z$1,0))</f>
